--- a/6月盘点汇总.xlsx
+++ b/6月盘点汇总.xlsx
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>クレ・ド・ポー ボーテ タンクッションエクラ ルミヌ</t>
+          <t>うる落ち水クレンジングアイメイクアップリムーバー ポイントメイク落とし 145ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4514254131312</t>
+          <t>4902806314946</t>
         </is>
       </c>
       <c r="D23" t="n">
